--- a/management/product backlog template_yuehanMeng.xlsx
+++ b/management/product backlog template_yuehanMeng.xlsx
@@ -1,22 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView windowWidth="11520" windowHeight="9780"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
-  <si>
-    <t/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="120">
   <si>
     <t>Story ID</t>
   </si>
@@ -125,6 +136,9 @@
     <t>As an Administrator, I want to receive AI-generated recommendations for balancing the workload among TAs, so that I can efficiently reassign tasks if someone is overbooked or underutilized.</t>
   </si>
   <si>
+    <t>Could</t>
+  </si>
+  <si>
     <t>AI Feature. AI outputs must not be blindly accepted; the system must provide explainable results and structured logic for its recommendations.</t>
   </si>
   <si>
@@ -184,7 +198,10 @@
     <t>Application History Archive</t>
   </si>
   <si>
-    <t>As an HR professional, I would like to store and retrieve the past TA application data and feedback information in a simple text format, and also be able to preserve the records for a long time.</t>
+    <t>As a human resources professional, I hope to view the TA application data in a simple text format, so that I can quickly check the status without using an interactive system, and be able to share it easily.</t>
+  </si>
+  <si>
+    <t>Chould</t>
   </si>
   <si>
     <t>Comply with the restrictions of "no use of database" and "data interoperability"</t>
@@ -234,9 +251,6 @@
     <t>As a Module Organiser, I want to create and update TA job posts, so that students can see accurate module details, requirements, deadlines, and vacancies.</t>
   </si>
   <si>
-    <t>must</t>
-  </si>
-  <si>
     <t>1. MO can create a TA job post. 2. MO can edit job details after posting. 3. Updated information is visible to applicants.</t>
   </si>
   <si>
@@ -318,9 +332,6 @@
 As a Module Organiser, I want to track the number of applicants, confirmed hires, and remaining vacancies in real time, so that I can manage recruitment progress more effectively.</t>
   </si>
   <si>
-    <t>should</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 1. System shows total applicants. 2. System shows confirmed hires. 3. System shows remaining vacancies.</t>
   </si>
@@ -390,14 +401,16 @@
     <t>Status tracking page.</t>
   </si>
   <si>
-    <t>US-D04</t>
-  </si>
-  <si>
-    <t>Input Validation Handler</t>
-  </si>
-  <si>
-    <t>As a Developer, I want to implement form validation for all user inputs,
-so that invalid data (empty fields, wrong formats) is rejected before saving.</t>
+    <t>US-T04</t>
+  </si>
+  <si>
+    <t>Form Input Validation Test</t>
+  </si>
+  <si>
+    <t>As a Tester, I want to verify that all user input forms (job posting, application submission, profile creation) correctly validate required fields and data formats, so that invalid or incomplete data is rejected before being saved to files.</t>
+  </si>
+  <si>
+    <t>Ensures data integrity.</t>
   </si>
   <si>
     <t>US-A06</t>
@@ -410,91 +423,195 @@
   </si>
   <si>
     <t>A foundational requirement for the entire system.</t>
-  </si>
-  <si>
-    <t>US-T04</t>
-  </si>
-  <si>
-    <t>Form Input Validation Test</t>
-  </si>
-  <si>
-    <t>As a Tester, I want to verify that all user input forms (job posting, application submission, profile creation) correctly validate required fields and data formats, so that invalid or incomplete data is rejected before being saved to files.</t>
-  </si>
-  <si>
-    <t>Ensures data integrity.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="300" formatCode="General"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="13">
-    <font>
+  <fonts count="24">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="等线"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <color rgb="FF175CEB"/>
-      <sz val="10"/>
-      <u/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Segoe UI Symbol"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-    </font>
-    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-    </font>
-    <font>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -502,20 +619,193 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill/>
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599994"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -525,124 +815,567 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
-    <border/>
-    <border diagonalUp="1" diagonalDown="1">
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs>
-    <xf numFmtId="300" fontId="3" fillId="0" borderId="4" xfId="0"/>
-    <xf numFmtId="300" fontId="3" fillId="5" borderId="4" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="300" fontId="3" fillId="5" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="300" fontId="3" fillId="5" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="27" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="300" fontId="3" fillId="0" borderId="4" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="27" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="3" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="5" fillId="3" borderId="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf fontId="7" fillId="3" borderId="0" xfId="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf fontId="5" fillId="3" borderId="0" xfId="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="300" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -927,570 +1660,595 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="J26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203" defaultRowHeight="15"/>
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.16406" style="26" customWidth="1"/>
-    <col min="2" max="2" width="16.6641" style="26" customWidth="1"/>
-    <col min="3" max="3" width="36" style="26" customWidth="1"/>
-    <col min="4" max="4" width="9.16406" style="26"/>
-    <col min="5" max="5" width="28.332" style="26" customWidth="1"/>
-    <col min="6" max="7" width="19.832" style="26" customWidth="1"/>
-    <col min="8" max="8" width="30.0508" style="26" customWidth="1"/>
-    <col min="9" max="9" width="24.832" style="26" customWidth="1"/>
-    <col min="10" max="10" width="26.332" style="26" customWidth="1"/>
+    <col min="1" max="1" width="9.16666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6666666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="36" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.16666666666667" style="1"/>
+    <col min="5" max="5" width="28.3333333333333" style="1" customWidth="1"/>
+    <col min="6" max="7" width="19.8333333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="30.0462962962963" style="1" customWidth="1"/>
+    <col min="9" max="9" width="24.8333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.3333333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16">
-      <c r="A1" s="4" t="s">
+    <row r="1" ht="28.8" spans="1:10">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="5" t="s">
+    </row>
+    <row r="2" ht="100.8" spans="1:10">
+      <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="3:6" ht="112">
-      <c r="C2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="6" t="s">
+    </row>
+    <row r="3" ht="57.6" spans="1:10">
+      <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="G3" s="1">
+        <v>5</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="9">
+    </row>
+    <row r="4" ht="57.6" spans="1:10">
+      <c r="A4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="1">
         <v>5</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="H4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="7" t="s"/>
-      <c r="G4" s="9">
+    </row>
+    <row r="5" ht="57.6" spans="1:10">
+      <c r="A5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" ht="89.25" customHeight="1" spans="1:10">
+      <c r="A6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="1">
+        <v>3</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" ht="87" customHeight="1" spans="1:10">
+      <c r="A7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="1">
         <v>8</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="H7" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" ht="88.5" customHeight="1" spans="1:10">
+      <c r="A8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="9">
+      <c r="G8" s="1">
+        <v>3</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" ht="87.75" customHeight="1" spans="1:10">
+      <c r="A9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="1">
+        <v>3</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" ht="88.5" customHeight="1" spans="1:10">
+      <c r="A10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" ht="72" spans="1:10">
+      <c r="A11" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="1">
         <v>5</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="89.25" customHeight="1">
-      <c r="A6" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="9" t="s"/>
-      <c r="E6" s="9" t="s"/>
-      <c r="F6" s="9" t="s"/>
-      <c r="G6" s="9" t="s"/>
-      <c r="H6" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="11" t="s"/>
-      <c r="J6" s="11" t="s"/>
-    </row>
-    <row r="7" spans="1:10" ht="87" customHeight="1">
-      <c r="A7" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="9" t="s"/>
-      <c r="E7" s="9" t="s"/>
-      <c r="F7" s="9" t="s"/>
-      <c r="G7" s="9" t="s"/>
-      <c r="H7" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="11" t="s"/>
-      <c r="J7" s="11" t="s"/>
-    </row>
-    <row r="8" spans="1:10" ht="88.5" customHeight="1">
-      <c r="A8" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="9" t="s"/>
-      <c r="E8" s="9" t="s"/>
-      <c r="F8" s="9" t="s"/>
-      <c r="G8" s="9" t="s"/>
-      <c r="H8" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8" s="11" t="s"/>
-      <c r="J8" s="11" t="s"/>
-    </row>
-    <row r="9" spans="1:10" ht="87.75" customHeight="1">
-      <c r="A9" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="9" t="s"/>
-      <c r="E9" s="9" t="s"/>
-      <c r="F9" s="9" t="s"/>
-      <c r="G9" s="9" t="s"/>
-      <c r="H9" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9" s="11" t="s"/>
-      <c r="J9" s="11" t="s"/>
-    </row>
-    <row r="10" spans="1:10" ht="88.5" customHeight="1">
-      <c r="A10" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="9" t="s"/>
-      <c r="E10" s="9" t="s"/>
-      <c r="F10" s="9" t="s"/>
-      <c r="G10" s="9" t="s"/>
-      <c r="H10" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="I10" s="11" t="s"/>
-      <c r="J10" s="11" t="s"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="9">
+      <c r="H11" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" ht="72" spans="1:10">
+      <c r="A12" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" ht="201.6" spans="1:10">
+      <c r="A13" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="1">
         <v>8</v>
       </c>
-      <c r="H11" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" s="9">
+      <c r="H13" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" ht="259.2" spans="1:10">
+      <c r="A14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="1">
         <v>3</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13" s="9">
-        <v>8</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G14" s="9">
+      <c r="H14" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" ht="86.4" spans="1:10">
+      <c r="A15" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="1">
         <v>3</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15" s="9" t="s"/>
-      <c r="H15" s="17" t="s">
+      <c r="H15" s="9" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="7" t="s">
+    <row r="16" ht="115.2" spans="1:10">
+      <c r="A16" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="G16" s="9" t="s"/>
-      <c r="H16" s="16" t="s">
+      <c r="G16" s="1">
+        <v>3</v>
+      </c>
+      <c r="H16" s="9" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="7" t="s">
+    <row r="17" ht="100.8" spans="1:10">
+      <c r="A17" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="16" t="s">
+      <c r="D17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="G17" s="9" t="s"/>
-      <c r="H17" s="16" t="s">
+      <c r="G17" s="1">
+        <v>2</v>
+      </c>
+      <c r="H17" s="9" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="7" t="s">
+    <row r="18" ht="115.2" spans="1:10">
+      <c r="A18" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" s="16" t="s">
+      <c r="D18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="G18" s="9" t="s"/>
-      <c r="H18" s="16" t="s">
+      <c r="G18" s="1">
+        <v>2</v>
+      </c>
+      <c r="H18" s="9" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="20" t="s">
+    <row r="19" ht="86.4" spans="1:10">
+      <c r="A19" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="F19" s="16" t="s">
+      <c r="G19" s="1">
+        <v>3</v>
+      </c>
+      <c r="H19" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G19" s="9" t="s"/>
-      <c r="H19" s="16" t="s">
+    </row>
+    <row r="20" ht="72" spans="1:10">
+      <c r="A20" s="5" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="7" t="s">
+      <c r="B20" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="C20" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="D20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5">
+        <v>3</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E20" s="7" t="s"/>
-      <c r="F20" s="7" t="s"/>
-      <c r="G20" s="7" t="s"/>
-      <c r="H20" s="24" t="s">
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" ht="57.6" spans="1:10">
+      <c r="A21" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="I20" s="7" t="s"/>
-      <c r="J20" s="7" t="s"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="7" t="s">
+      <c r="B21" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="C21" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="D21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5">
+        <v>3</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="7" t="s"/>
-      <c r="F21" s="7" t="s"/>
-      <c r="G21" s="7" t="s"/>
-      <c r="H21" s="24" t="s">
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" ht="72" spans="1:10">
+      <c r="A22" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="I21" s="7" t="s"/>
-      <c r="J21" s="7" t="s"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="7" t="s">
+      <c r="B22" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="C22" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="D22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5">
+        <v>2</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E22" s="7" t="s"/>
-      <c r="F22" s="7" t="s"/>
-      <c r="G22" s="7" t="s"/>
-      <c r="H22" s="24" t="s">
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" ht="43.2" spans="1:10">
+      <c r="A23" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="I22" s="7" t="s"/>
-      <c r="J22" s="7" t="s"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="7" t="s">
+      <c r="B23" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="C23" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="D23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5">
+        <v>3</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" s="7" t="s"/>
-      <c r="F23" s="7" t="s"/>
-      <c r="G23" s="7" t="s"/>
-      <c r="H23" s="24" t="s">
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+    </row>
+    <row r="24" ht="72" spans="1:10">
+      <c r="A24" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="I23" s="7" t="s"/>
-      <c r="J23" s="7" t="s"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="7" t="s">
+      <c r="B24" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="C24" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="D24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5">
+        <v>2</v>
+      </c>
+      <c r="H24" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E24" s="7" t="s"/>
-      <c r="F24" s="7" t="s"/>
-      <c r="G24" s="7" t="s"/>
-      <c r="H24" s="24" t="s">
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+    </row>
+    <row r="25" ht="86.4" spans="1:10">
+      <c r="A25" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="I24" s="7" t="s"/>
-      <c r="J24" s="7" t="s"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E25" s="7" t="s"/>
-      <c r="F25" s="7" t="s"/>
-      <c r="G25" s="7" t="s"/>
-      <c r="H25" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="I25" s="7" t="s"/>
-      <c r="J25" s="7" t="s"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="7" t="s">
+      <c r="B25" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5">
+        <v>3</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+    </row>
+    <row r="26" ht="86.4" spans="1:10">
+      <c r="A26" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="H26" s="7" t="s">
+      <c r="D26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" s="1">
+        <v>5</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>119</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/management/product backlog template_yuehanMeng.xlsx
+++ b/management/product backlog template_yuehanMeng.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11520" windowHeight="9780"/>
+    <workbookView windowWidth="23040" windowHeight="9767"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="119">
   <si>
     <t>Story ID</t>
   </si>
@@ -198,10 +198,7 @@
     <t>Application History Archive</t>
   </si>
   <si>
-    <t>As a human resources professional, I hope to view the TA application data in a simple text format, so that I can quickly check the status without using an interactive system, and be able to share it easily.</t>
-  </si>
-  <si>
-    <t>Chould</t>
+    <t>As a hr professional, I hope to view the TA application data in a simple text format, so that I can quickly check the status without using an interactive system, and be able to share it easily.</t>
   </si>
   <si>
     <t>Comply with the restrictions of "no use of database" and "data interoperability"</t>
@@ -1912,185 +1909,185 @@
         <v>53</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="G12" s="1">
         <v>2</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="201.6" spans="1:10">
       <c r="A13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G13" s="1">
         <v>8</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" ht="259.2" spans="1:10">
       <c r="A14" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G14" s="1">
         <v>3</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" ht="86.4" spans="1:10">
       <c r="A15" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="C15" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>68</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G15" s="1">
         <v>3</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" ht="115.2" spans="1:10">
       <c r="A16" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="C16" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="D16" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="F16" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" ht="100.8" spans="1:10">
       <c r="A17" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="C17" s="9" t="s">
         <v>78</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>79</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G17" s="1">
         <v>2</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" ht="115.2" spans="1:10">
       <c r="A18" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="C18" s="9" t="s">
         <v>83</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>84</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G18" s="1">
         <v>2</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" ht="86.4" spans="1:10">
       <c r="A19" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G19" s="1">
         <v>3</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:10">
       <c r="A20" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>94</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>15</v>
@@ -2101,20 +2098,20 @@
         <v>3</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
     </row>
     <row r="21" ht="57.6" spans="1:10">
       <c r="A21" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>15</v>
@@ -2125,20 +2122,20 @@
         <v>3</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
     </row>
     <row r="22" ht="72" spans="1:10">
       <c r="A22" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>102</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>15</v>
@@ -2149,20 +2146,20 @@
         <v>2</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
     </row>
     <row r="23" ht="43.2" spans="1:10">
       <c r="A23" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>106</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>15</v>
@@ -2173,20 +2170,20 @@
         <v>3</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
     </row>
     <row r="24" ht="72" spans="1:10">
       <c r="A24" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>110</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>24</v>
@@ -2197,20 +2194,20 @@
         <v>2</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
     </row>
     <row r="25" ht="86.4" spans="1:10">
       <c r="A25" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>114</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>15</v>
@@ -2221,20 +2218,20 @@
         <v>3</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
     </row>
     <row r="26" ht="86.4" spans="1:10">
       <c r="A26" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>118</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>15</v>
@@ -2243,7 +2240,7 @@
         <v>5</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/management/product backlog template_yuehanMeng.xlsx
+++ b/management/product backlog template_yuehanMeng.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9767"/>
+    <workbookView windowWidth="15240" windowHeight="4452"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -184,8 +184,7 @@
     <t>Overall Recruitment Monitoring</t>
   </si>
   <si>
-    <t>As a school administrator,
-I hope to monitor the recruitment progress of all subject modules on a dashboard, so that I can keep track of the vacancies in teaching positions.</t>
+    <t>As a school head,I hope to deploy a system that does not require database configuration and has very little server maintenance, so that we can reduce the financial cost and technical barrier of the project.</t>
   </si>
   <si>
     <t>From a global management perspective, solve the problem of statistical opacity.</t>
@@ -198,7 +197,7 @@
     <t>Application History Archive</t>
   </si>
   <si>
-    <t>As a hr professional, I hope to view the TA application data in a simple text format, so that I can quickly check the status without using an interactive system, and be able to share it easily.</t>
+    <t>As the administrative supervisor, I would like to obtain the standard plain text versions of all TA application histories, so as to keep offline records for auditing purposes and be able to easily share the data with other departments.</t>
   </si>
   <si>
     <t>Comply with the restrictions of "no use of database" and "data interoperability"</t>
@@ -432,7 +431,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -455,13 +454,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -926,146 +918,146 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1878,7 +1870,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" ht="72" spans="1:10">
+    <row r="11" ht="86.4" spans="1:10">
       <c r="A11" s="8" t="s">
         <v>47</v>
       </c>
@@ -1892,13 +1884,13 @@
         <v>15</v>
       </c>
       <c r="G11" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="12" ht="72" spans="1:10">
+    <row r="12" ht="86.4" spans="1:10">
       <c r="A12" s="5" t="s">
         <v>51</v>
       </c>

--- a/management/product backlog template_yuehanMeng.xlsx
+++ b/management/product backlog template_yuehanMeng.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15240" windowHeight="4452"/>
+    <workbookView windowWidth="23040" windowHeight="9767"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -181,13 +181,13 @@
     <t>US-C01</t>
   </si>
   <si>
-    <t>Overall Recruitment Monitoring</t>
+    <t>The demand for low-cost deployment</t>
   </si>
   <si>
     <t>As a school head,I hope to deploy a system that does not require database configuration and has very little server maintenance, so that we can reduce the financial cost and technical barrier of the project.</t>
   </si>
   <si>
-    <t>From a global management perspective, solve the problem of statistical opacity.</t>
+    <t>Enables low-cost deployment that requires no database installation and minimal maintenance.</t>
   </si>
   <si>
     <t xml:space="preserve">US-C02
@@ -200,7 +200,7 @@
     <t>As the administrative supervisor, I would like to obtain the standard plain text versions of all TA application histories, so as to keep offline records for auditing purposes and be able to easily share the data with other departments.</t>
   </si>
   <si>
-    <t>Comply with the restrictions of "no use of database" and "data interoperability"</t>
+    <t>By exporting data in simple plain text format, one can directly view and share it without relying on the database system.</t>
   </si>
   <si>
     <t>US-D03</t>
